--- a/public/data/pricing_special.xlsx
+++ b/public/data/pricing_special.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>60687f88-79bc-45a7-9908-2cf88a35e27d</v>
+        <v>11f717dc-f999-496d-8608-1632858bfc47</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D2" t="str">
         <v>CTR-001-001</v>
@@ -466,18 +466,18 @@
         <v>2025-01-01</v>
       </c>
       <c r="K2" t="str">
-        <v>2025-12-31</v>
+        <v>2026-03-01</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>667536ba-f830-4627-862f-8ef4cbe22723</v>
+        <v>e6a09bcd-21dc-4c4d-95fb-2e9b53a009b7</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C3" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D3" t="str">
         <v>CTR-001-001</v>
@@ -501,179 +501,179 @@
         <v>2025-01-01</v>
       </c>
       <c r="K3" t="str">
-        <v>2025-12-31</v>
+        <v>2026-03-01</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>6a9449b1-0794-442f-af83-f57fef774d0e</v>
+        <v>699ce08a-3f8f-4be6-b7ae-51714b4b5632</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C4" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D4" t="str">
-        <v>CTR-002-001</v>
+        <v>CTR-001-002</v>
       </c>
       <c r="E4" t="str">
-        <v>FAM trips</v>
+        <v>VIP Guest</v>
       </c>
       <c r="F4" t="str">
         <v>Percentage</v>
       </c>
       <c r="G4">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="H4">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="I4" t="str">
-        <v>Approved travel agents only</v>
+        <v>Platinum loyalty members</v>
       </c>
       <c r="J4" t="str">
-        <v>2025-03-01</v>
+        <v>2025-06-01</v>
       </c>
       <c r="K4" t="str">
-        <v>2026-02-28</v>
+        <v>2026-05-31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>4b8f50f8-6127-4c4a-be62-477191b129c6</v>
+        <v>69a3abc7-cc92-4650-8da0-91f9db0b9c76</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C5" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D5" t="str">
-        <v>CTR-003-001</v>
+        <v>CTR-002-001</v>
       </c>
       <c r="E5" t="str">
-        <v>Management</v>
+        <v>FAM trips</v>
       </c>
       <c r="F5" t="str">
         <v>Percentage</v>
       </c>
       <c r="G5">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H5">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I5" t="str">
-        <v>Soneva executives</v>
+        <v>Approved travel agents only</v>
       </c>
       <c r="J5" t="str">
-        <v>2025-06-01</v>
+        <v>2025-03-01</v>
       </c>
       <c r="K5" t="str">
-        <v>2026-05-31</v>
+        <v>2027-02-28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>c3e7d4c3-3452-42ca-860c-e704395df27d</v>
+        <v>132edc10-ee01-4f2c-8c0a-caa2dcdaf811</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C6" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D6" t="str">
         <v>CTR-003-001</v>
       </c>
       <c r="E6" t="str">
-        <v>Journalists</v>
+        <v>Management</v>
       </c>
       <c r="F6" t="str">
         <v>Percentage</v>
       </c>
       <c r="G6">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="I6" t="str">
-        <v>Pre-approved media only</v>
+        <v>Soneva executives</v>
       </c>
       <c r="J6" t="str">
         <v>2025-06-01</v>
       </c>
       <c r="K6" t="str">
-        <v>2026-05-31</v>
+        <v>2027-05-31</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>d77c6eab-e446-4668-9814-8c6c4036f4b0</v>
+        <v>79834d0e-835c-4662-9c62-ea5221057102</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D7" t="str">
-        <v>CTR-005-001</v>
+        <v>CTR-003-001</v>
       </c>
       <c r="E7" t="str">
-        <v>Tour Operators</v>
+        <v>Journalists</v>
       </c>
       <c r="F7" t="str">
-        <v>Absolute</v>
+        <v>Percentage</v>
       </c>
       <c r="G7">
-        <v>490</v>
+        <v>75</v>
       </c>
       <c r="H7">
-        <v>285</v>
+        <v>75</v>
       </c>
       <c r="I7" t="str">
-        <v>Min 10 pax per group</v>
+        <v>Pre-approved media only</v>
       </c>
       <c r="J7" t="str">
-        <v>2025-04-01</v>
+        <v>2025-06-01</v>
       </c>
       <c r="K7" t="str">
-        <v>2026-03-31</v>
+        <v>2027-05-31</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>c0a3b580-8665-4745-a5aa-3dc6471d3b60</v>
+        <v>2becd8f6-84ac-4055-ae79-43d162b885aa</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C8" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D8" t="str">
-        <v>CTR-006-001</v>
+        <v>CTR-003-002</v>
       </c>
       <c r="E8" t="str">
-        <v>Management</v>
+        <v>Staff</v>
       </c>
       <c r="F8" t="str">
-        <v>Percentage</v>
+        <v>Absolute</v>
       </c>
       <c r="G8">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H8">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="I8" t="str">
-        <v>FS executives</v>
+        <v>Soneva staff</v>
       </c>
       <c r="J8" t="str">
-        <v>2026-01-01</v>
+        <v>2025-06-01</v>
       </c>
       <c r="K8" t="str">
         <v>2026-12-31</v>
@@ -681,86 +681,86 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>4d45d9c8-dcd3-4463-94e0-2169acfdb543</v>
+        <v>3744239a-e3e6-4df4-ad4f-afe10c877806</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C9" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D9" t="str">
-        <v>CTR-006-001</v>
+        <v>CTR-003-003</v>
       </c>
       <c r="E9" t="str">
-        <v>Staff</v>
+        <v>Management</v>
       </c>
       <c r="F9" t="str">
-        <v>Absolute</v>
+        <v>Percentage</v>
       </c>
       <c r="G9">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="H9">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="I9" t="str">
-        <v>Resort staff</v>
+        <v>Soneva board members</v>
       </c>
       <c r="J9" t="str">
-        <v>2026-01-01</v>
+        <v>2025-10-01</v>
       </c>
       <c r="K9" t="str">
-        <v>2026-12-31</v>
+        <v>2026-09-30</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>23594767-3b93-4896-8b19-7f0af61db863</v>
+        <v>0f882d89-d3a7-40ed-8ac9-2ae1cd3aba80</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C10" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D10" t="str">
-        <v>CTR-006-001</v>
+        <v>CTR-005-001</v>
       </c>
       <c r="E10" t="str">
-        <v>FAM trips</v>
+        <v>Tour Operators</v>
       </c>
       <c r="F10" t="str">
-        <v>Percentage</v>
+        <v>Absolute</v>
       </c>
       <c r="G10">
-        <v>50</v>
+        <v>490</v>
       </c>
       <c r="H10">
-        <v>50</v>
+        <v>285</v>
       </c>
       <c r="I10" t="str">
-        <v>Approved agents</v>
+        <v>Min 10 pax per group</v>
       </c>
       <c r="J10" t="str">
-        <v>2026-01-01</v>
+        <v>2025-04-01</v>
       </c>
       <c r="K10" t="str">
-        <v>2026-12-31</v>
+        <v>2027-03-31</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>096934b4-a391-4838-9481-b211d9fab99b</v>
+        <v>c0d8a6de-11bb-4a75-99b7-8c095e85b5c0</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C11" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D11" t="str">
-        <v>CTR-008-001</v>
+        <v>CTR-005-002</v>
       </c>
       <c r="E11" t="str">
         <v>Management</v>
@@ -775,62 +775,62 @@
         <v>100</v>
       </c>
       <c r="I11" t="str">
-        <v>Minor Hotels executive team</v>
+        <v>Marriott VP and above</v>
       </c>
       <c r="J11" t="str">
-        <v>2025-10-01</v>
+        <v>2025-11-01</v>
       </c>
       <c r="K11" t="str">
-        <v>2026-09-30</v>
+        <v>2026-10-31</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>feafa19b-3d0d-4c26-b7a3-8aff561eff55</v>
+        <v>6b3e9f74-2b1d-4c4c-a1db-2fb0b42ea8a8</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C12" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D12" t="str">
-        <v>CTR-008-001</v>
+        <v>CTR-006-001</v>
       </c>
       <c r="E12" t="str">
-        <v>Tour Guides</v>
+        <v>Management</v>
       </c>
       <c r="F12" t="str">
-        <v>Absolute</v>
+        <v>Percentage</v>
       </c>
       <c r="G12">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I12" t="str">
-        <v>Licensed Maldives tour guides</v>
+        <v>FS executives</v>
       </c>
       <c r="J12" t="str">
-        <v>2025-10-01</v>
+        <v>2025-01-01</v>
       </c>
       <c r="K12" t="str">
-        <v>2026-09-30</v>
+        <v>2027-12-31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>9cc541dc-870f-4223-bd98-79996b9e272d</v>
+        <v>6ed05daa-d443-492a-a012-d799176637ad</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C13" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D13" t="str">
-        <v>CTR-009-001</v>
+        <v>CTR-006-001</v>
       </c>
       <c r="E13" t="str">
         <v>Staff</v>
@@ -839,59 +839,304 @@
         <v>Absolute</v>
       </c>
       <c r="G13">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="H13">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="I13" t="str">
-        <v>RC staff with employee badge</v>
+        <v>Resort staff</v>
       </c>
       <c r="J13" t="str">
-        <v>2025-11-01</v>
+        <v>2025-01-01</v>
       </c>
       <c r="K13" t="str">
-        <v>2026-10-31</v>
+        <v>2027-12-31</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>0d01b58b-a407-4fc2-a4ee-450affbb04b0</v>
+        <v>0bac89b3-5f02-4ce1-b4d8-e44404837d85</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="C14" t="str">
-        <v>2026-02-14T10:22:02.382Z</v>
+        <v>2026-02-15T07:01:23.175Z</v>
       </c>
       <c r="D14" t="str">
+        <v>CTR-006-001</v>
+      </c>
+      <c r="E14" t="str">
+        <v>FAM trips</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Percentage</v>
+      </c>
+      <c r="G14">
+        <v>50</v>
+      </c>
+      <c r="H14">
+        <v>50</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Approved agents</v>
+      </c>
+      <c r="J14" t="str">
+        <v>2025-01-01</v>
+      </c>
+      <c r="K14" t="str">
+        <v>2027-12-31</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>440031ac-e24e-4b9a-9026-e8a02a27e908</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C15" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D15" t="str">
+        <v>CTR-006-002</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Journalists</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Percentage</v>
+      </c>
+      <c r="G15">
+        <v>70</v>
+      </c>
+      <c r="H15">
+        <v>70</v>
+      </c>
+      <c r="I15" t="str">
+        <v>Accredited media</v>
+      </c>
+      <c r="J15" t="str">
+        <v>2025-06-01</v>
+      </c>
+      <c r="K15" t="str">
+        <v>2027-05-31</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>0c762f0d-b233-497c-8ac5-b7004ee3bbc8</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C16" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D16" t="str">
+        <v>CTR-006-003</v>
+      </c>
+      <c r="E16" t="str">
+        <v>VIP Guest</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Percentage</v>
+      </c>
+      <c r="G16">
+        <v>85</v>
+      </c>
+      <c r="H16">
+        <v>85</v>
+      </c>
+      <c r="I16" t="str">
+        <v>FS Private Jet guests</v>
+      </c>
+      <c r="J16" t="str">
+        <v>2026-01-01</v>
+      </c>
+      <c r="K16" t="str">
+        <v>2026-12-31</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>a1a7ab30-fb87-4525-9dc8-db84837d8057</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C17" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D17" t="str">
+        <v>CTR-008-001</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Management</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Percentage</v>
+      </c>
+      <c r="G17">
+        <v>100</v>
+      </c>
+      <c r="H17">
+        <v>100</v>
+      </c>
+      <c r="I17" t="str">
+        <v>Minor Hotels executive team</v>
+      </c>
+      <c r="J17" t="str">
+        <v>2025-10-01</v>
+      </c>
+      <c r="K17" t="str">
+        <v>2027-09-30</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>deb4acad-764d-4e62-8d28-38ed1f1186bb</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C18" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D18" t="str">
+        <v>CTR-008-001</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Tour Guides</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Absolute</v>
+      </c>
+      <c r="G18">
+        <v>200</v>
+      </c>
+      <c r="H18">
+        <v>120</v>
+      </c>
+      <c r="I18" t="str">
+        <v>Licensed Maldives tour guides</v>
+      </c>
+      <c r="J18" t="str">
+        <v>2025-10-01</v>
+      </c>
+      <c r="K18" t="str">
+        <v>2027-09-30</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>1926d4be-76c6-4626-a248-cffe755a5b70</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C19" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D19" t="str">
+        <v>CTR-008-002</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Staff</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Absolute</v>
+      </c>
+      <c r="G19">
+        <v>140</v>
+      </c>
+      <c r="H19">
+        <v>85</v>
+      </c>
+      <c r="I19" t="str">
+        <v>Anantara resort staff</v>
+      </c>
+      <c r="J19" t="str">
+        <v>2025-10-01</v>
+      </c>
+      <c r="K19" t="str">
+        <v>2026-09-30</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>30d0d506-39c6-4c13-8915-266b045908b3</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C20" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D20" t="str">
         <v>CTR-009-001</v>
       </c>
-      <c r="E14" t="str">
+      <c r="E20" t="str">
+        <v>Staff</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Absolute</v>
+      </c>
+      <c r="G20">
+        <v>100</v>
+      </c>
+      <c r="H20">
+        <v>60</v>
+      </c>
+      <c r="I20" t="str">
+        <v>RC staff with employee badge</v>
+      </c>
+      <c r="J20" t="str">
+        <v>2025-11-01</v>
+      </c>
+      <c r="K20" t="str">
+        <v>2026-10-31</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>379229b6-7a17-4a2e-ac74-a09a189016d1</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="C21" t="str">
+        <v>2026-02-15T07:01:23.175Z</v>
+      </c>
+      <c r="D21" t="str">
+        <v>CTR-009-001</v>
+      </c>
+      <c r="E21" t="str">
         <v>Advertisers</v>
       </c>
-      <c r="F14" t="str">
-        <v>Percentage</v>
-      </c>
-      <c r="G14">
+      <c r="F21" t="str">
+        <v>Percentage</v>
+      </c>
+      <c r="G21">
         <v>60</v>
       </c>
-      <c r="H14">
+      <c r="H21">
         <v>60</v>
       </c>
-      <c r="I14" t="str">
+      <c r="I21" t="str">
         <v>Approved brand partners</v>
       </c>
-      <c r="J14" t="str">
+      <c r="J21" t="str">
         <v>2025-11-01</v>
       </c>
-      <c r="K14" t="str">
+      <c r="K21" t="str">
         <v>2026-10-31</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K21"/>
   </ignoredErrors>
 </worksheet>
 </file>